--- a/branches/effective-period-master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/effective-period-master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$121</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4670" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4287" uniqueCount="570">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T11:48:03+00:00</t>
+    <t>2026-10-09T12:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1445,20 +1445,14 @@
     <t>Zeitpunkt, zu dem die gemessene Eigenschaft im Probenmaterial (e.g. Analytkonzentration) mutmaßlich der Eigenschaft im Patienten entsprach. 
 Wenn der Zeitpunkt der Probenentnahme angegeben ist, wird meist dieser Zeitpunkt verwendet. 
 Andernfalls wird zumeist behelfsmäßig der Probeneingang im Labor gewählt. 
-Dieses Element ist wichtig um verschiedene Analysen im Zeitverlauf sortieren zu können.</t>
+Dieses Element ist wichtig um verschiedene Analysen im Zeitverlauf sortieren zu können.
+Stammen die Untersuchungen aus mehreren Proben oder wurde eine Probe über einen Zeitraum gewonnen (z. B. 24-Stunden-Sammelurin), ist es ein Zeitraum.</t>
   </si>
   <si>
     <t>If the diagnostic procedure was performed on the patient, this is the time it was performed. If there are specimens, the diagnostically relevant time can be derived from the specimen collection times, but the specimen information is not always available, and the exact relationship between the specimens and the diagnostically relevant time is not always automatic.</t>
   </si>
   <si>
     <t>Need to know where in the patient history to file/present this report.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1490,129 +1484,6 @@
   </si>
   <si>
     <t>Datum der Probenentnahme | Datum des Eingangs der Probe im Labor</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectiveDateTime</t>
-  </si>
-  <si>
-    <t>effectiveDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Klinischer Bezugszeitpunkt des Laborbefunds, in der Regel der Zeitpunkt der Probenentnahme.</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectiveDateTime.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectiveDateTime.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectiveDateTime.extension:QuelleKlinischesBezugsdatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectiveDateTime.value</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x].value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectivePeriod</t>
-  </si>
-  <si>
-    <t>effectivePeriod</t>
-  </si>
-  <si>
-    <t>Klinischer Bezugszeitraum</t>
-  </si>
-  <si>
-    <t>Klinischer Bezugszeitraum des Laborbefunds, wenn die Probe über einen Zeitraum gewonnen wurde, z. B. 24-Stunden-Sammelurin.</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectivePeriod.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectivePeriod.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectivePeriod.extension:QuelleKlinischesBezugsdatum</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectivePeriod.start</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x].start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x]:effectivePeriod.end</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.effective[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>DR.2</t>
   </si>
   <si>
     <t>DiagnosticReport.issued</t>
@@ -2254,10 +2125,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM132"/>
+  <dimension ref="A1:AM121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="71.375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.33984375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.53515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.5234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
@@ -11643,7 +11514,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>451</v>
       </c>
@@ -11720,14 +11591,16 @@
         <v>79</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AC85" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>451</v>
@@ -11745,21 +11618,21 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11865,10 +11738,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11976,13 +11849,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B88" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -12004,13 +11877,13 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12087,20 +11960,18 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>88</v>
@@ -12115,17 +11986,19 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12174,7 +12047,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12189,53 +12062,57 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>460</v>
+        <v>79</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>462</v>
+        <v>475</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>79</v>
+        <v>477</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>102</v>
+        <v>478</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
       </c>
@@ -12283,36 +12160,36 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>105</v>
+        <v>476</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>79</v>
+        <v>484</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12323,7 +12200,7 @@
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>79</v>
@@ -12335,13 +12212,13 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>478</v>
+        <v>103</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>479</v>
+        <v>104</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12380,29 +12257,31 @@
         <v>79</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC91" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>79</v>
@@ -12414,28 +12293,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>79</v>
@@ -12444,15 +12321,17 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>467</v>
+        <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>468</v>
+        <v>109</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -12489,16 +12368,16 @@
         <v>79</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>115</v>
@@ -12510,7 +12389,7 @@
         <v>78</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>481</v>
+        <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>116</v>
@@ -12525,12 +12404,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12544,24 +12423,26 @@
         <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>472</v>
+        <v>102</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>484</v>
+        <v>346</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -12610,7 +12491,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>486</v>
+        <v>349</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12619,10 +12500,10 @@
         <v>88</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>79</v>
@@ -12634,18 +12515,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>452</v>
+        <v>79</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12655,7 +12534,7 @@
         <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>79</v>
@@ -12664,20 +12543,18 @@
         <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>321</v>
+        <v>129</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>489</v>
+        <v>352</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>490</v>
+        <v>353</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>79</v>
       </c>
@@ -12701,13 +12578,13 @@
         <v>79</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>79</v>
@@ -12725,7 +12602,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>451</v>
+        <v>357</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -12740,21 +12617,21 @@
         <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>460</v>
+        <v>79</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>461</v>
+        <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>462</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12768,24 +12645,26 @@
         <v>88</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>103</v>
+        <v>359</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -12834,7 +12713,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>105</v>
+        <v>362</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12846,7 +12725,7 @@
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
@@ -12860,21 +12739,21 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>79</v>
@@ -12883,19 +12762,19 @@
         <v>79</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>110</v>
+        <v>365</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>111</v>
+        <v>366</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12933,31 +12812,31 @@
         <v>79</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>115</v>
+        <v>367</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>79</v>
@@ -12969,46 +12848,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J97" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K97" t="s" s="2">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
       </c>
@@ -13056,7 +12937,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>115</v>
+        <v>492</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -13068,24 +12949,24 @@
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>79</v>
+        <v>497</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13096,30 +12977,32 @@
         <v>77</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>502</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
       </c>
@@ -13167,16 +13050,16 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>500</v>
+        <v>79</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>100</v>
@@ -13185,7 +13068,7 @@
         <v>79</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>79</v>
@@ -13193,10 +13076,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13216,27 +13099,23 @@
         <v>79</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>472</v>
+        <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>504</v>
+        <v>103</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q99" t="s" s="2">
-        <v>507</v>
-      </c>
+      <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
         <v>79</v>
       </c>
@@ -13280,7 +13159,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>508</v>
+        <v>105</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13289,63 +13168,61 @@
         <v>88</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>500</v>
+        <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>509</v>
+        <v>79</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>511</v>
+        <v>107</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>512</v>
+        <v>109</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>513</v>
+        <v>110</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>79</v>
       </c>
@@ -13381,59 +13258,59 @@
         <v>79</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>510</v>
+        <v>115</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>516</v>
+        <v>79</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>517</v>
+        <v>79</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>519</v>
+        <v>79</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>89</v>
@@ -13445,20 +13322,18 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>520</v>
+        <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>521</v>
+        <v>346</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>522</v>
+        <v>347</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>79</v>
       </c>
@@ -13506,36 +13381,36 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>518</v>
+        <v>349</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>525</v>
+        <v>79</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>526</v>
+        <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>527</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13555,18 +13430,20 @@
         <v>79</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>103</v>
+        <v>352</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -13591,13 +13468,13 @@
         <v>79</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>79</v>
@@ -13615,7 +13492,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>105</v>
+        <v>357</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13627,7 +13504,7 @@
         <v>79</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>79</v>
@@ -13639,44 +13516,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>109</v>
+        <v>359</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>110</v>
+        <v>360</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>111</v>
+        <v>361</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13714,31 +13591,31 @@
         <v>79</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>115</v>
+        <v>362</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>79</v>
@@ -13750,12 +13627,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13769,7 +13646,7 @@
         <v>88</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>79</v>
@@ -13781,13 +13658,13 @@
         <v>102</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13837,7 +13714,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -13846,7 +13723,7 @@
         <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>100</v>
@@ -13861,46 +13738,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>79</v>
+        <v>512</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>129</v>
+        <v>513</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>352</v>
+        <v>514</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>353</v>
+        <v>515</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
       </c>
@@ -13924,13 +13803,13 @@
         <v>79</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>79</v>
@@ -13948,13 +13827,13 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>357</v>
+        <v>511</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>79</v>
@@ -13966,18 +13845,18 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>79</v>
+        <v>518</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13991,26 +13870,24 @@
         <v>88</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>359</v>
+        <v>103</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -14059,7 +13936,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14071,7 +13948,7 @@
         <v>79</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>79</v>
@@ -14085,21 +13962,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>79</v>
@@ -14108,19 +13985,19 @@
         <v>79</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>364</v>
+        <v>109</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>365</v>
+        <v>110</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14158,31 +14035,31 @@
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>367</v>
+        <v>115</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>79</v>
@@ -14194,26 +14071,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>535</v>
+        <v>79</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>79</v>
@@ -14222,20 +14099,18 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>520</v>
+        <v>102</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>536</v>
+        <v>346</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>537</v>
+        <v>347</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>79</v>
       </c>
@@ -14283,36 +14158,36 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>534</v>
+        <v>349</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>525</v>
+        <v>79</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>539</v>
+        <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>527</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14323,32 +14198,30 @@
         <v>77</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J109" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K109" t="s" s="2">
-        <v>541</v>
+        <v>129</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>542</v>
+        <v>352</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>543</v>
+        <v>353</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>79</v>
       </c>
@@ -14372,13 +14245,13 @@
         <v>79</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>79</v>
@@ -14396,13 +14269,13 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>540</v>
+        <v>357</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>79</v>
@@ -14414,7 +14287,7 @@
         <v>79</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>546</v>
+        <v>79</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>79</v>
@@ -14422,10 +14295,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14445,18 +14318,20 @@
         <v>79</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>103</v>
+        <v>359</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>79</v>
@@ -14505,7 +14380,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>105</v>
+        <v>362</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14517,7 +14392,7 @@
         <v>79</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>79</v>
@@ -14531,21 +14406,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>548</v>
+        <v>524</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>548</v>
+        <v>524</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>79</v>
@@ -14554,19 +14429,19 @@
         <v>79</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>110</v>
+        <v>365</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>111</v>
+        <v>366</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14604,31 +14479,31 @@
         <v>79</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>115</v>
+        <v>367</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>79</v>
@@ -14640,12 +14515,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14656,28 +14531,28 @@
         <v>77</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>102</v>
+        <v>526</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>346</v>
+        <v>527</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>347</v>
+        <v>528</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>348</v>
+        <v>529</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14727,16 +14602,16 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>349</v>
+        <v>525</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>100</v>
@@ -14753,21 +14628,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>79</v>
+        <v>531</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -14779,18 +14654,18 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>129</v>
+        <v>532</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>352</v>
+        <v>533</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>79</v>
       </c>
@@ -14814,13 +14689,13 @@
         <v>79</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>79</v>
@@ -14838,13 +14713,13 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>357</v>
+        <v>530</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>79</v>
@@ -14856,18 +14731,18 @@
         <v>79</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>79</v>
+        <v>536</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14881,26 +14756,24 @@
         <v>88</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>359</v>
+        <v>103</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>79</v>
@@ -14949,7 +14822,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -14961,7 +14834,7 @@
         <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>79</v>
@@ -14975,21 +14848,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>79</v>
@@ -14998,19 +14871,19 @@
         <v>79</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>364</v>
+        <v>109</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>365</v>
+        <v>110</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>366</v>
+        <v>111</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15060,19 +14933,19 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>367</v>
+        <v>115</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>79</v>
@@ -15084,47 +14957,47 @@
         <v>79</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I116" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I116" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="J116" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>555</v>
+        <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>558</v>
+        <v>111</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>559</v>
+        <v>191</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -15173,7 +15046,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15185,13 +15058,13 @@
         <v>79</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>560</v>
+        <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>79</v>
@@ -15199,10 +15072,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15228,13 +15101,17 @@
         <v>102</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>103</v>
+        <v>545</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>79</v>
       </c>
@@ -15282,7 +15159,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>105</v>
+        <v>544</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -15294,7 +15171,7 @@
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
@@ -15308,21 +15185,21 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>79</v>
@@ -15331,20 +15208,18 @@
         <v>79</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>108</v>
+        <v>550</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>109</v>
+        <v>551</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>79</v>
@@ -15381,31 +15256,31 @@
         <v>79</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>115</v>
+        <v>549</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>79</v>
@@ -15419,14 +15294,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>79</v>
+        <v>554</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -15442,21 +15317,21 @@
         <v>79</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>346</v>
+        <v>555</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O119" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
       </c>
@@ -15504,7 +15379,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>349</v>
+        <v>553</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -15513,7 +15388,7 @@
         <v>88</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>100</v>
@@ -15522,7 +15397,7 @@
         <v>79</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>79</v>
+        <v>558</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>79</v>
@@ -15530,10 +15405,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15544,7 +15419,7 @@
         <v>77</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>79</v>
@@ -15553,20 +15428,18 @@
         <v>79</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>352</v>
+        <v>560</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>79</v>
@@ -15591,13 +15464,13 @@
         <v>79</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>355</v>
+        <v>562</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>356</v>
+        <v>563</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>79</v>
@@ -15615,13 +15488,13 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>357</v>
+        <v>559</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>79</v>
@@ -15633,7 +15506,7 @@
         <v>79</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>79</v>
+        <v>558</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>79</v>
@@ -15641,10 +15514,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15655,7 +15528,7 @@
         <v>77</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>79</v>
@@ -15664,21 +15537,23 @@
         <v>79</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>195</v>
+        <v>565</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>359</v>
+        <v>566</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>360</v>
+        <v>567</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O121" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
       </c>
@@ -15726,13 +15601,13 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>362</v>
+        <v>564</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>79</v>
@@ -15744,1235 +15619,14 @@
         <v>79</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>79</v>
+        <v>558</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AM132" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM132">
+  <autoFilter ref="A1:AM121">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16982,7 +15636,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI131">
+  <conditionalFormatting sqref="A2:AI120">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
